--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,7 +174,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -274,12 +274,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -289,12 +289,12 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3922</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -304,12 +304,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.0499</t>
+          <t>-0.0421</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.0878</t>
+          <t>-0.0794</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -331,7 +331,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,7 +488,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:GOQASy66</t>
+          <t>flashscore:zs3PZaZa</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -508,154 +508,154 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t/>
+          <t>1.7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t/>
+          <t>2.15</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.3097</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2084</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.4819</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.7151</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.7306</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t/>
+          <t>away</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t/>
+          <t>3.229</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t/>
+          <t>4.798</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t/>
+          <t>2.075</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t/>
+          <t>2.4</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t/>
+          <t>3.4</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t/>
+          <t>2.88</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.4167</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.3472</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t/>
+          <t>-0.107</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t/>
+          <t>-0.0857</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>ready_for_phase_5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Phase 3 status was upstream_blocked.</t>
+          <t>Probabilities + fair odds attached; market joined.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>flashscore:zs3PZaZa</t>
+          <t>flashscore:rTwrFuZR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -690,37 +690,37 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.2111</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.2084</t>
+          <t>0.2192</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.4819</t>
+          <t>0.5697</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.7151</t>
+          <t>0.5694</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.7306</t>
+          <t>0.5838</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -730,62 +730,62 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>3.229</t>
+          <t>4.737</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>4.798</t>
+          <t>4.562</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2.075</t>
+          <t>1.755</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.4167</t>
+          <t>0.1538</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2174</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.3472</t>
+          <t>0.6944</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.107</t>
+          <t>0.0573</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.0857</t>
+          <t>0.0018</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>-0.1247</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -794,163 +794,6 @@
         </is>
       </c>
       <c r="AE5" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-04 06:57:12 ACST</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>flashscore:rTwrFuZR</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>0.2111</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0.2192</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0.5697</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0.5694</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0.5838</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>4.737</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>4.562</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>1.755</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>4.6</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0.1538</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0.2174</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0.6944</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>0.0573</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>0.0018</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>-0.1247</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
         <is>
           <t>Probabilities + fair odds attached; market joined.</t>
         </is>
@@ -1123,7 +966,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1223,12 +1066,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1238,12 +1081,12 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3922</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1253,12 +1096,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.0499</t>
+          <t>-0.0421</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.0878</t>
+          <t>-0.0794</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1280,7 +1123,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1437,7 +1280,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1922,7 +1765,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2071,163 +1914,6 @@
         </is>
       </c>
       <c r="AE2" t="inlineStr">
-        <is>
-          <t>Phase 3 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-04 06:57:12 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flashscore:GOQASy66</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Almeria</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Mirandes</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
         <is>
           <t>Phase 3 status was upstream_blocked.</t>
         </is>
@@ -2260,7 +1946,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
     </row>
@@ -2284,7 +1970,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2296,7 +1982,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2018,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,7 +174,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -274,47 +274,47 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.3922</t>
+          <t>0.4167</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t>0.3636</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.0421</t>
+          <t>-0.0666</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.0794</t>
+          <t>-0.0878</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.0619</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -331,7 +331,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,7 +488,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -645,7 +645,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,7 +966,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1066,47 +1066,47 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.3922</t>
+          <t>0.4167</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t>0.3636</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.0421</t>
+          <t>-0.0666</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.0794</t>
+          <t>-0.0878</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.0619</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -1123,7 +1123,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1765,7 +1765,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,7 +174,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -274,7 +274,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -284,12 +284,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.4167</t>
+          <t>0.4202</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -299,12 +299,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.3636</t>
+          <t>0.3571</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.0666</t>
+          <t>-0.0701</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -314,7 +314,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.0865</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -331,7 +331,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,7 +488,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -645,7 +645,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,7 +966,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.4167</t>
+          <t>0.4202</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.3636</t>
+          <t>0.3571</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.0666</t>
+          <t>-0.0701</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.0865</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -1123,7 +1123,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1765,7 +1765,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,17 +174,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:2qevfSqS</t>
+          <t>flashscore:n1pZG14F</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -194,154 +194,154 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t/>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t/>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.3501</t>
+          <t/>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t/>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.4436</t>
+          <t/>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.7427</t>
+          <t/>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.7591</t>
+          <t/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>away</t>
+          <t/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2.856</t>
+          <t/>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>4.847</t>
+          <t/>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.254</t>
+          <t/>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t/>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t/>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t/>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.4202</t>
+          <t/>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t/>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.3571</t>
+          <t/>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.0701</t>
+          <t/>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.0878</t>
+          <t/>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.0865</t>
+          <t/>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>ready_for_phase_5</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Probabilities + fair odds attached; market joined.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:n1pZG14F</t>
+          <t>flashscore:2qevfSqS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -351,17 +351,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -488,7 +488,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -645,7 +645,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.2174</t>
+          <t>0.2222</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.0018</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -966,37 +966,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:2qevfSqS</t>
+          <t>flashscore:zs3PZaZa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.3501</t>
+          <t>0.3097</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t>0.2084</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.4436</t>
+          <t>0.4819</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.7427</t>
+          <t>0.7151</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.7591</t>
+          <t>0.7306</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -1051,22 +1051,22 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2.856</t>
+          <t>3.229</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>4.847</t>
+          <t>4.798</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.254</t>
+          <t>2.075</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.4202</t>
+          <t>0.4167</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.3571</t>
+          <t>0.3472</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.0701</t>
+          <t>-0.107</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.0878</t>
+          <t>-0.0857</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.0865</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -1123,17 +1123,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:zs3PZaZa</t>
+          <t>flashscore:rTwrFuZR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1168,37 +1168,37 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.2111</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.2084</t>
+          <t>0.2192</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.4819</t>
+          <t>0.5697</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.7151</t>
+          <t>0.5694</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.7306</t>
+          <t>0.5838</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1208,62 +1208,62 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>3.229</t>
+          <t>4.737</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>4.798</t>
+          <t>4.562</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2.075</t>
+          <t>1.755</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4167</t>
+          <t>0.1538</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2222</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.3472</t>
+          <t>0.6944</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.107</t>
+          <t>0.0573</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.0857</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>-0.1247</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1272,163 +1272,6 @@
         </is>
       </c>
       <c r="AE3" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-04 07:34:23 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>flashscore:rTwrFuZR</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.2111</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.2192</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.5697</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.5694</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.5838</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>4.737</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>4.562</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>1.755</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>4.6</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0.1538</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0.2174</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.6944</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>0.0573</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>0.0018</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>-0.1247</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
         <is>
           <t>Probabilities + fair odds attached; market joined.</t>
         </is>
@@ -1765,7 +1608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1914,6 +1757,163 @@
         </is>
       </c>
       <c r="AE2" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-04 11:09:27 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>flashscore:2qevfSqS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Austin FC</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Phase 3 status was upstream_blocked.</t>
         </is>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,626 +174,312 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:27 ACST</t>
+          <t>2026-05-05 01:24:50 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:n1pZG14F</t>
+          <t>flashscore:zs3PZaZa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t/>
+          <t>1.7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t/>
+          <t>2.15</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.3097</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2084</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.4819</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.7151</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.7306</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t/>
+          <t>away</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t/>
+          <t>3.229</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t/>
+          <t>4.798</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t/>
+          <t>2.075</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t/>
+          <t>2.45</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t/>
+          <t>3.3</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t/>
+          <t>2.88</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.4082</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.303</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.3472</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t/>
+          <t>-0.0985</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t/>
+          <t>-0.0946</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>ready_for_phase_5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Phase 3 status was upstream_blocked.</t>
+          <t>Probabilities + fair odds attached; market joined.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:27 ACST</t>
+          <t>2026-05-05 01:24:50 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:2qevfSqS</t>
+          <t>flashscore:rTwrFuZR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t/>
+          <t>1.1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t/>
+          <t>1.95</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2111</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2192</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.5697</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.5694</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.5838</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t/>
+          <t>away</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t/>
+          <t>4.737</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t/>
+          <t>4.562</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t/>
+          <t>1.755</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t/>
+          <t>6.5</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t/>
+          <t>4.5</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t/>
+          <t>1.44</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.1538</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2222</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.6944</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0573</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t/>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t/>
+          <t>-0.1247</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>ready_for_phase_5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
-        <is>
-          <t>Phase 3 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-04 11:09:27 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>flashscore:zs3PZaZa</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.3097</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.2084</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.4819</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.7151</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.7306</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>3.229</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>4.798</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2.075</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0.4167</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0.2941</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.3472</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>-0.107</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.0857</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-04 11:09:27 ACST</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>flashscore:rTwrFuZR</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.2111</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0.2192</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0.5697</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0.5694</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0.5838</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>4.737</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>4.562</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>1.755</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0.1538</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0.2222</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0.6944</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>0.0573</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-0.003</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>-0.1247</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
         <is>
           <t>Probabilities + fair odds attached; market joined.</t>
         </is>
@@ -966,7 +652,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:27 ACST</t>
+          <t>2026-05-05 01:24:50 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1066,12 +752,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1081,12 +767,12 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.4167</t>
+          <t>0.4082</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1096,12 +782,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.107</t>
+          <t>-0.0985</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.0857</t>
+          <t>-0.0946</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,7 +809,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:27 ACST</t>
+          <t>2026-05-05 01:24:50 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1605,320 +1291,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-04 11:09:27 ACST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>flashscore:n1pZG14F</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Chelsea</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Nottingham</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Phase 3 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-04 11:09:27 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flashscore:2qevfSqS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Austin FC</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>St. Louis City</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Phase 3 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1946,7 +1318,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:27 ACST</t>
+          <t>2026-05-05 01:24:50 ACST</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1342,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1354,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2018,7 +1390,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,7 +174,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:50 ACST</t>
+          <t>2026-05-05 01:28:49 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -331,7 +331,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:50 ACST</t>
+          <t>2026-05-05 01:28:49 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -652,7 +652,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:50 ACST</t>
+          <t>2026-05-05 01:28:49 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -809,7 +809,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:50 ACST</t>
+          <t>2026-05-05 01:28:49 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:50 ACST</t>
+          <t>2026-05-05 01:28:49 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,314 +174,785 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:28:49 ACST</t>
+          <t>2026-05-06 01:40:49 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:zs3PZaZa</t>
+          <t>16072838</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Roda JC Kerkrade</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t/>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t/>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t/>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.2084</t>
+          <t/>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.4819</t>
+          <t/>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.7151</t>
+          <t/>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.7306</t>
+          <t/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>away</t>
+          <t/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>3.229</t>
+          <t/>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>4.798</t>
+          <t/>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.075</t>
+          <t/>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t/>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t/>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t/>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.4082</t>
+          <t/>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t/>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.3472</t>
+          <t/>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.0985</t>
+          <t/>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.0946</t>
+          <t/>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t/>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>ready_for_phase_5</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Probabilities + fair odds attached; market joined.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05 01:28:49 ACST</t>
+          <t>2026-05-06 01:40:49 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:rTwrFuZR</t>
+          <t>16115678</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:49 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>15632635</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.2111</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.2192</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.5697</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0.5694</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0.5838</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>4.737</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>4.562</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>1.755</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.1538</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.2222</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.6944</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.0573</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.003</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>-0.1247</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined.</t>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:49 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>16115794</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Almere City FC</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>De Graafschap</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:49 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>15632634</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FC Bayern München</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
@@ -649,320 +1120,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-05 01:28:49 ACST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>flashscore:zs3PZaZa</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.3097</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.2084</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.4819</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0.7151</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0.7306</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>3.229</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>4.798</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2.075</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.4082</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0.303</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.3472</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>-0.0985</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-0.0946</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-05 01:28:49 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flashscore:rTwrFuZR</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.2111</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.2192</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.5697</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0.5694</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0.5838</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>4.737</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>4.562</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>1.755</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.1538</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.2222</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.6944</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.0573</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.003</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>-0.1247</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1291,6 +1448,791 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:49 ACST</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>16072838</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Roda JC Kerkrade</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:49 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>16115678</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:49 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>15632635</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:49 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>16115794</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Almere City FC</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>De Graafschap</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:49 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>15632634</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FC Bayern München</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1318,7 +2260,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:28:49 ACST</t>
+          <t>2026-05-06 01:40:49 ACST</t>
         </is>
       </c>
     </row>
@@ -1342,7 +2284,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1354,7 +2296,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1366,7 +2308,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1390,7 +2332,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1402,7 +2344,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Proceed with Phase 5 for ready_for_phase_5 rows.</t>
+          <t>No ready predictions; check Phase 2/3 outputs.</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,7 +174,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -331,7 +331,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -341,12 +341,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16115678</t>
+          <t>16115794</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -356,12 +356,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City FC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -488,7 +488,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -498,12 +498,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15632635</t>
+          <t>15632634</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -513,12 +513,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FC Bayern München</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Paris Saint-Germain</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -645,37 +645,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16115794</t>
+          <t>14065245</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02:15</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Almere City FC</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -802,155 +802,783 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15632634</t>
+          <t>14064514</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>RC Lens</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:58 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>16116799</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>FC Bayern München</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Paris Saint-Germain</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>upstream_blocked</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:58 ACST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>14083568</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Levante UD</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:58 ACST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>16116800</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:58 ACST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>14024024</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Liverpool FC</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
         <is>
           <t>Phase 3 status was upstream_blocked.</t>
         </is>
@@ -1451,7 +2079,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1608,7 +2236,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1618,12 +2246,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16115678</t>
+          <t>16115794</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1633,12 +2261,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City FC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1765,7 +2393,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1775,12 +2403,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15632635</t>
+          <t>15632634</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1790,12 +2418,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FC Bayern München</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Paris Saint-Germain</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1922,37 +2550,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16115794</t>
+          <t>14065245</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02:15</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Almere City FC</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2079,155 +2707,783 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15632634</t>
+          <t>14064514</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>RC Lens</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:58 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>16116799</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>FC Bayern München</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Paris Saint-Germain</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>upstream_blocked</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:58 ACST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>14083568</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Levante UD</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:58 ACST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>16116800</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:58 ACST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>14024024</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Liverpool FC</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
         <is>
           <t>Phase 3 status was upstream_blocked.</t>
         </is>
@@ -2260,7 +3516,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
     </row>
@@ -2284,7 +3540,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2296,7 +3552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2332,7 +3588,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,17 +174,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:I9QHhKRp</t>
+          <t>flashscore:vyaxjXte</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -194,52 +194,52 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Ath. Bilbao</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t/>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t/>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.5246938973246565</t>
+          <t/>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.2460460014461316</t>
+          <t/>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.22926010122921187</t>
+          <t/>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -254,84 +254,84 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1.906</t>
+          <t/>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>4.064</t>
+          <t/>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>4.362</t>
+          <t/>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t/>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t/>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t/>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.5263</t>
+          <t/>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t/>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t/>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.0016</t>
+          <t/>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.0481</t>
+          <t/>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>-0.0207</t>
+          <t/>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>ready_for_phase_5</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.9064 edge_delta=0.0364.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -341,7 +341,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:vyaxjXte</t>
+          <t>flashscore:n12plBB7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -356,12 +356,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ath Bilbao</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -481,14 +481,14 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Phase 3 status was upstream_blocked.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:n12plBB7</t>
+          <t>flashscore:0OhvAhYQ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -513,12 +513,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -645,7 +645,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>flashscore:0OhvAhYQ</t>
+          <t>flashscore:K8ZA4Wel</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -670,47 +670,47 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t/>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t/>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.4066501701323252</t>
+          <t/>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.29282514177693764</t>
+          <t/>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.3005246880907373</t>
+          <t/>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -725,84 +725,84 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>draw</t>
+          <t/>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2.459</t>
+          <t/>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>3.415</t>
+          <t/>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>3.328</t>
+          <t/>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t/>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t/>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t/>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.4167</t>
+          <t/>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.3472</t>
+          <t/>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t/>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t/>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.0544</t>
+          <t/>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.0148</t>
+          <t/>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>ready_for_phase_5</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.8248 edge_delta=0.0364.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>flashscore:K8ZA4Wel</t>
+          <t>flashscore:YFVo6qXh</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -827,47 +827,47 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t/>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t/>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.45667677255069306</t>
+          <t/>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.26031479903085275</t>
+          <t/>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.28300842841845425</t>
+          <t/>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -882,84 +882,84 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t/>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>3.842</t>
+          <t/>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>3.533</t>
+          <t/>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t/>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t/>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t/>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.4878</t>
+          <t/>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t/>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.2778</t>
+          <t/>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.0311</t>
+          <t/>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.0338</t>
+          <t/>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.0052</t>
+          <t/>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>ready_for_phase_5</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.8248 edge_delta=0.0364.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>flashscore:YFVo6qXh</t>
+          <t>flashscore:C0sw852t</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -984,47 +984,47 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t/>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t/>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.40954225477395045</t>
+          <t/>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.30484146854803174</t>
+          <t/>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.2856162766780178</t>
+          <t/>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1039,84 +1039,84 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>draw</t>
+          <t/>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2.442</t>
+          <t/>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t/>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>3.501</t>
+          <t/>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t/>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t/>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t/>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.4762</t>
+          <t/>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.3636</t>
+          <t/>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.2381</t>
+          <t/>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.0667</t>
+          <t/>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.0588</t>
+          <t/>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.0475</t>
+          <t/>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>ready_for_phase_5</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.8248 edge_delta=0.0364.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>flashscore:C0sw852t</t>
+          <t>flashscore:llRR0leD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>flashscore:hMXI2AQ0</t>
+          <t>flashscore:ttZg4N15</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1298,47 +1298,47 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t/>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t/>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.4372567093235832</t>
+          <t/>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.2687266910420475</t>
+          <t/>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.29401659963436927</t>
+          <t/>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1353,84 +1353,84 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2.287</t>
+          <t/>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>3.721</t>
+          <t/>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3.401</t>
+          <t/>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t/>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t/>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t/>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t/>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t/>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.2703</t>
+          <t/>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.0627</t>
+          <t/>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.017</t>
+          <t/>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.0237</t>
+          <t/>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>ready_for_phase_5</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.8248 edge_delta=0.0364.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>flashscore:llRR0leD</t>
+          <t>flashscore:hMXI2AQ0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1455,47 +1455,47 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Vallecano</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t/>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t/>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.3807064536741214</t>
+          <t/>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.28600984025559106</t>
+          <t/>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.3332837060702875</t>
+          <t/>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1510,94 +1510,94 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>draw</t>
+          <t/>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2.627</t>
+          <t/>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>3.496</t>
+          <t/>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t/>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t/>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t/>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t/>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.4167</t>
+          <t/>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.3125</t>
+          <t/>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t/>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.036</t>
+          <t/>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.0265</t>
+          <t/>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.0107</t>
+          <t/>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>ready_for_phase_5</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.8248 edge_delta=0.0364.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>flashscore:ttZg4N15</t>
+          <t>flashscore:YH84GNJi</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1607,52 +1607,52 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t/>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t/>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.3268357679180888</t>
+          <t/>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.2693994539249147</t>
+          <t/>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.4037647781569966</t>
+          <t/>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1667,84 +1667,84 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>away</t>
+          <t/>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t/>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>3.712</t>
+          <t/>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2.477</t>
+          <t/>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t/>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t/>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t/>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t/>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.2778</t>
+          <t/>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.4762</t>
+          <t/>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.0238</t>
+          <t/>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.0084</t>
+          <t/>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>-0.0724</t>
+          <t/>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>ready_for_phase_5</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.8248 edge_delta=0.0364.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>flashscore:YH84GNJi</t>
+          <t>flashscore:nmmS8WHr</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1769,47 +1769,47 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t/>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t/>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.3721816236162362</t>
+          <t/>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.2918172447724477</t>
+          <t/>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.3360011316113161</t>
+          <t/>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1824,84 +1824,84 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>draw</t>
+          <t/>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2.687</t>
+          <t/>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>3.427</t>
+          <t/>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2.976</t>
+          <t/>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t/>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t/>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t/>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>0.4348</t>
+          <t/>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t/>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t/>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.0626</t>
+          <t/>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.0415</t>
+          <t/>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t/>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>ready_for_phase_5</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.9064 edge_delta=0.0364.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>flashscore:nmmS8WHr</t>
+          <t>flashscore:h0IS6Ane</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1926,47 +1926,47 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t/>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t/>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.43150495052825755</t>
+          <t/>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0.2964484420593661</t>
+          <t/>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.27204660741237635</t>
+          <t/>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1981,94 +1981,94 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2.317</t>
+          <t/>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>3.373</t>
+          <t/>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3.676</t>
+          <t/>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t/>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t/>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t/>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t/>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t/>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.3636</t>
+          <t/>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.0498</t>
+          <t/>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.0262</t>
+          <t/>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>-0.0916</t>
+          <t/>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>ready_for_phase_5</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.9064 edge_delta=0.0364.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>flashscore:h0IS6Ane</t>
+          <t>flashscore:prPnPy9r</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2078,52 +2078,52 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t/>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t/>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.5228536976696226</t>
+          <t/>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.2565021159001856</t>
+          <t/>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.22064418643019182</t>
+          <t/>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2138,84 +2138,84 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.913</t>
+          <t/>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>3.899</t>
+          <t/>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>4.532</t>
+          <t/>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t/>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t/>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t/>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0.4082</t>
+          <t/>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t/>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t/>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.1147</t>
+          <t/>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.0661</t>
+          <t/>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>-0.1127</t>
+          <t/>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>ready_for_phase_5</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.9064 edge_delta=0.0364.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>flashscore:prPnPy9r</t>
+          <t>flashscore:IXv8WJG8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2240,22 +2240,22 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2365,14 +2365,14 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>Phase 3 status was partial_form.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>flashscore:IXv8WJG8</t>
+          <t>flashscore:r1cGQTSk</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2397,47 +2397,47 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t/>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t/>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.5808847743813683</t>
+          <t/>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.2341648617176128</t>
+          <t/>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.18495036390101893</t>
+          <t/>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2452,84 +2452,84 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.722</t>
+          <t/>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t/>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>5.407</t>
+          <t/>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t/>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t/>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t/>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>0.7353</t>
+          <t/>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>0.2105</t>
+          <t/>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t/>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.1544</t>
+          <t/>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.0237</t>
+          <t/>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>0.0674</t>
+          <t/>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>ready_for_phase_5</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.9064 edge_delta=0.0364.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>flashscore:r1cGQTSk</t>
+          <t>flashscore:OhrGQlpm</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2554,47 +2554,47 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t/>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t/>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.4516464966096222</t>
+          <t/>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.24490244752986762</t>
+          <t/>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.30345105586051013</t>
+          <t/>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2609,84 +2609,84 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2.214</t>
+          <t/>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>4.083</t>
+          <t/>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>3.295</t>
+          <t/>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t/>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t/>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t/>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>0.3922</t>
+          <t/>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t/>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t/>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.0594</t>
+          <t/>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.0408</t>
+          <t/>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>-0.0782</t>
+          <t/>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>ready_for_phase_5</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.9064 edge_delta=0.0364.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>flashscore:OhrGQlpm</t>
+          <t>flashscore:xbwdLg87</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2711,47 +2711,47 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t/>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t/>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.59873893143366</t>
+          <t/>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.19696813891362425</t>
+          <t/>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.20429292965271595</t>
+          <t/>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2766,84 +2766,84 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t/>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>5.077</t>
+          <t/>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>4.895</t>
+          <t/>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t/>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t/>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t/>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>0.5882</t>
+          <t/>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>0.2381</t>
+          <t/>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.2222</t>
+          <t/>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.0105</t>
+          <t/>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.0411</t>
+          <t/>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>-0.0179</t>
+          <t/>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>ready_for_phase_5</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.9064 edge_delta=0.0364.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>flashscore:xbwdLg87</t>
+          <t>flashscore:z9FNO7c2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2868,22 +2868,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2993,14 +2993,14 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Phase 3 status was partial_form.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>flashscore:z9FNO7c2</t>
+          <t>flashscore:QcrGUcoL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3025,47 +3025,47 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t/>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t/>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.40455739606570673</t>
+          <t/>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.24994438856215778</t>
+          <t/>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.3454982153721355</t>
+          <t/>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -3080,84 +3080,84 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2.472</t>
+          <t/>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>4.001</t>
+          <t/>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2.894</t>
+          <t/>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t/>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t/>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t/>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>0.3922</t>
+          <t/>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t/>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.3846</t>
+          <t/>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.0124</t>
+          <t/>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.0358</t>
+          <t/>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>-0.0391</t>
+          <t/>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>ready_for_phase_5</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.9064 edge_delta=0.0364.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>flashscore:QcrGUcoL</t>
+          <t>flashscore:IeNfNFwe</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3182,47 +3182,47 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Paris FC</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t/>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t/>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.6650522463261022</t>
+          <t/>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.18945557732680196</t>
+          <t/>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.14549217634709588</t>
+          <t/>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -3237,84 +3237,84 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t/>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>5.278</t>
+          <t/>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>6.873</t>
+          <t/>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t/>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t/>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t/>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.7812</t>
+          <t/>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.1818</t>
+          <t/>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t/>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.1161</t>
+          <t/>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.0077</t>
+          <t/>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.0402</t>
+          <t/>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>ready_for_phase_5</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.9064 edge_delta=0.0364.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>flashscore:IeNfNFwe</t>
+          <t>flashscore:44Vsqc0E</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3339,12 +3339,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paris FC</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3464,24 +3464,24 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>Phase 3 status was upstream_blocked.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>flashscore:44Vsqc0E</t>
+          <t>flashscore:SduXBE3E</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3491,52 +3491,52 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t/>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t/>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.4294426966292135</t>
+          <t/>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.23142202247191013</t>
+          <t/>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.33913528089887646</t>
+          <t/>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -3551,94 +3551,94 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2.329</t>
+          <t/>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>4.321</t>
+          <t/>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2.949</t>
+          <t/>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t/>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t/>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t/>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t/>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t/>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.4762</t>
+          <t/>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.0961</t>
+          <t/>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.0186</t>
+          <t/>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>-0.1371</t>
+          <t/>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>ready_for_phase_5</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.9064 edge_delta=0.0364.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>flashscore:SduXBE3E</t>
+          <t>flashscore:I9QHhKRp</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3648,52 +3648,52 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t/>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t/>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.5474302114803626</t>
+          <t/>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.23065987915407857</t>
+          <t/>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.22190990936555893</t>
+          <t/>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -3708,77 +3708,77 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.827</t>
+          <t/>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>4.335</t>
+          <t/>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>4.506</t>
+          <t/>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t/>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t/>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t/>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.7692</t>
+          <t/>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.1667</t>
+          <t/>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t/>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-0.2218</t>
+          <t/>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t/>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.0969</t>
+          <t/>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>ready_for_phase_5</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.8248 edge_delta=0.0364.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
@@ -3946,2675 +3946,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>flashscore:I9QHhKRp</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Atalanta</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.5246938973246565</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.2460460014461316</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.22926010122921187</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>1.906</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>4.064</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>4.362</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.5263</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0.2941</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>-0.0016</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-0.0481</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>-0.0207</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.9064 edge_delta=0.0364.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flashscore:0OhvAhYQ</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Elche</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Getafe</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.4066501701323252</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.29282514177693764</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.3005246880907373</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>draw</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2.459</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>3.415</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>3.328</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.4167</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.3472</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.2857</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.0544</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0.0148</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.8248 edge_delta=0.0364.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>flashscore:K8ZA4Wel</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Levante</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Mallorca</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.45667677255069306</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.26031479903085275</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.28300842841845425</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>3.842</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>3.533</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0.4878</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0.2941</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.2778</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>-0.0311</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.0338</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>0.0052</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.8248 edge_delta=0.0364.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>flashscore:YFVo6qXh</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Osasuna</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Espanyol</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.40954225477395045</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0.30484146854803174</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0.2856162766780178</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>draw</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2.442</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>3.28</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>3.501</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0.4762</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0.3636</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0.2381</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-0.0667</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-0.0588</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>0.0475</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.8248 edge_delta=0.0364.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>flashscore:hMXI2AQ0</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Rayo Vallecano</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Villarreal</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>0.4372567093235832</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0.2687266910420475</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0.29401659963436927</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2.287</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>3.721</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>3.401</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>3.7</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0.2857</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0.2703</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>-0.0627</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>-0.017</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>0.0237</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.8248 edge_delta=0.0364.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>flashscore:llRR0leD</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>0.3807064536741214</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0.28600984025559106</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0.3332837060702875</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>draw</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>2.627</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>3.496</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0.4167</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0.3125</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0.3226</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>-0.036</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.0265</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>0.0107</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.8248 edge_delta=0.0364.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>flashscore:ttZg4N15</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Real Madrid</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>0.3268357679180888</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>0.2693994539249147</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0.4037647781569966</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>3.712</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2.477</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0.303</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0.2778</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0.4762</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>0.0238</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>-0.0084</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>-0.0724</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.8248 edge_delta=0.0364.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>flashscore:YH84GNJi</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>04:15</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0.3721816236162362</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0.2918172447724477</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0.3360011316113161</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>draw</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>2.687</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>3.427</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2.976</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0.4348</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0.3333</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0.303</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>-0.0626</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>-0.0415</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>0.033</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.9064 edge_delta=0.0364.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>flashscore:nmmS8WHr</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>04:15</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Sassuolo</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Lecce</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0.43150495052825755</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.2964484420593661</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0.27204660741237635</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2.317</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>3.373</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>3.676</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0.3817</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0.3226</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0.3636</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>0.0498</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>-0.0262</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>-0.0916</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.9064 edge_delta=0.0364.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>flashscore:h0IS6Ane</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>04:15</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Cremonese</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.5228536976696226</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.2565021159001856</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.22064418643019182</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>1.913</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>3.899</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>4.532</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0.4082</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>0.3226</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>0.3333</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>0.1147</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>-0.0661</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>-0.1127</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.9064 edge_delta=0.0364.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>flashscore:IXv8WJG8</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>0.5808847743813683</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>0.2341648617176128</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0.18495036390101893</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1.722</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>4.27</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>5.407</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>0.7353</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>0.2105</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>0.1176</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>-0.1544</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>0.0237</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>0.0674</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.9064 edge_delta=0.0364.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>flashscore:r1cGQTSk</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Lorient</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>0.4516464966096222</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>0.24490244752986762</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0.30345105586051013</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>2.214</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>4.083</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>3.295</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>0.3922</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>0.2857</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>0.3817</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>0.0594</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>-0.0408</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>-0.0782</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.9064 edge_delta=0.0364.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>flashscore:OhrGQlpm</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>0.59873893143366</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>0.19696813891362425</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0.20429292965271595</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>5.077</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>4.895</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>0.5882</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>0.2381</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>0.2222</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>0.0105</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>-0.0411</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>-0.0179</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.9064 edge_delta=0.0364.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>flashscore:z9FNO7c2</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>0.40455739606570673</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>0.24994438856215778</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0.3454982153721355</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2.472</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>4.001</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>2.894</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>2.6</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>0.3922</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>0.2857</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>0.3846</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>0.0124</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>-0.0358</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>-0.0391</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.9064 edge_delta=0.0364.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>flashscore:QcrGUcoL</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>0.6650522463261022</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>0.18945557732680196</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0.14549217634709588</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>1.504</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>5.278</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>6.873</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>0.7812</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>0.1818</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>0.1053</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>-0.1161</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>0.0077</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>0.0402</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.9064 edge_delta=0.0364.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>flashscore:44Vsqc0E</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>0.4294426966292135</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>0.23142202247191013</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>0.33913528089887646</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>2.329</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>4.321</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2.949</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>0.3333</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>0.4762</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>0.0961</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>-0.0186</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>-0.1371</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.9064 edge_delta=0.0364.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>flashscore:SduXBE3E</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>04:45</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Betis</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>0.5474302114803626</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>0.23065987915407857</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>0.22190990936555893</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>1.827</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>4.335</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>4.506</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>0.7692</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>0.1667</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>0.125</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>-0.2218</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>0.064</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>0.0969</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>ready_for_phase_5</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>Probabilities + fair odds attached; market joined. Winner blended with no-vig bookmaker probabilities at 40% weight. Calibration trust=0.8248 edge_delta=0.0364.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -6946,7 +4277,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6971,7 +4302,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ath Bilbao</t>
+          <t>Ath. Bilbao</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -7103,7 +4434,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7260,7 +4591,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -7270,7 +4601,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:C0sw852t</t>
+          <t>flashscore:0OhvAhYQ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -7285,12 +4616,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7417,17 +4748,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>flashscore:prPnPy9r</t>
+          <t>flashscore:K8ZA4Wel</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -7437,27 +4768,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -7567,24 +4898,24 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Phase 3 status was partial_form.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>flashscore:xbwdLg87</t>
+          <t>flashscore:YFVo6qXh</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7594,27 +4925,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -7724,162 +5055,2831 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Phase 3 status was partial_form.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>flashscore:C0sw852t</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Oviedo</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-18 04:09:11 ACST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>flashscore:llRR0leD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-18 04:09:11 ACST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>flashscore:ttZg4N15</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-18 04:09:11 ACST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>flashscore:hMXI2AQ0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vallecano</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-18 04:09:11 ACST</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>flashscore:YH84GNJi</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-18 04:09:11 ACST</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>flashscore:nmmS8WHr</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-18 04:09:11 ACST</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>flashscore:h0IS6Ane</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-18 04:09:11 ACST</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>Ligue 1</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>flashscore:prPnPy9r</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-18 04:09:11 ACST</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>flashscore:IXv8WJG8</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-18 04:09:11 ACST</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>flashscore:r1cGQTSk</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lorient</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-18 04:09:11 ACST</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>flashscore:OhrGQlpm</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-18 04:09:11 ACST</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>flashscore:xbwdLg87</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-18 04:09:11 ACST</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>flashscore:z9FNO7c2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-18 04:09:11 ACST</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>flashscore:QcrGUcoL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-18 04:09:11 ACST</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>flashscore:IeNfNFwe</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Paris FC</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>PSG</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
         <is>
           <t>upstream_blocked</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-18 04:09:11 ACST</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>flashscore:44Vsqc0E</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-18 04:09:11 ACST</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>flashscore:SduXBE3E</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-18 04:09:11 ACST</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>flashscore:I9QHhKRp</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
         <is>
           <t>Phase 3 status was upstream_blocked.</t>
         </is>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
     </row>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-18 01:53:08 ACST</t>
+          <t>2026-05-18 04:06:59 ACST</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Proceed with Phase 5 for ready_for_phase_5 rows.</t>
+          <t>No ready predictions; check Phase 2/3 outputs.</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,17 +174,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:vyaxjXte</t>
+          <t>flashscore:YH84GNJi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -194,17 +194,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ath. Bilbao</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -324,24 +324,24 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Phase 3 status was upstream_blocked.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:n12plBB7</t>
+          <t>flashscore:nmmS8WHr</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -351,17 +351,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -488,17 +488,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:0OhvAhYQ</t>
+          <t>flashscore:h0IS6Ane</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -508,17 +508,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -645,17 +645,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>flashscore:K8ZA4Wel</t>
+          <t>flashscore:prPnPy9r</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -665,17 +665,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -802,17 +802,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>flashscore:YFVo6qXh</t>
+          <t>flashscore:IXv8WJG8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -822,17 +822,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -959,17 +959,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>flashscore:C0sw852t</t>
+          <t>flashscore:r1cGQTSk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -979,17 +979,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1109,24 +1109,24 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>flashscore:llRR0leD</t>
+          <t>flashscore:OhrGQlpm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>Phase 3 status was upstream_blocked.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>flashscore:ttZg4N15</t>
+          <t>flashscore:xbwdLg87</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1293,17 +1293,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1430,17 +1430,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>flashscore:hMXI2AQ0</t>
+          <t>flashscore:QcrGUcoL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vallecano</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1587,17 +1587,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>flashscore:YH84GNJi</t>
+          <t>flashscore:IeNfNFwe</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1607,17 +1607,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Paris FC</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1737,24 +1737,24 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>flashscore:nmmS8WHr</t>
+          <t>flashscore:44Vsqc0E</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1764,17 +1764,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1901,17 +1901,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>flashscore:h0IS6Ane</t>
+          <t>flashscore:SduXBE3E</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2058,17 +2058,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>flashscore:prPnPy9r</t>
+          <t>flashscore:vyaxjXte</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2078,17 +2078,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Ath. Bilbao</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2208,24 +2208,24 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>flashscore:IXv8WJG8</t>
+          <t>flashscore:n12plBB7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2235,17 +2235,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2365,24 +2365,24 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>flashscore:r1cGQTSk</t>
+          <t>flashscore:0OhvAhYQ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2392,17 +2392,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2522,24 +2522,24 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>flashscore:OhrGQlpm</t>
+          <t>flashscore:K8ZA4Wel</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2549,17 +2549,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2679,24 +2679,24 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>flashscore:xbwdLg87</t>
+          <t>flashscore:YFVo6qXh</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2706,17 +2706,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>flashscore:z9FNO7c2</t>
+          <t>flashscore:C0sw852t</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2863,17 +2863,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2993,24 +2993,24 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>flashscore:QcrGUcoL</t>
+          <t>flashscore:llRR0leD</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3020,17 +3020,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3150,24 +3150,24 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>flashscore:IeNfNFwe</t>
+          <t>flashscore:ttZg4N15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3177,17 +3177,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paris FC</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3314,17 +3314,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>flashscore:44Vsqc0E</t>
+          <t>flashscore:hMXI2AQ0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3334,17 +3334,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Vallecano</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3464,24 +3464,24 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>flashscore:SduXBE3E</t>
+          <t>flashscore:z9FNO7c2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3491,17 +3491,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3621,14 +3621,14 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4277,17 +4277,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:vyaxjXte</t>
+          <t>flashscore:YH84GNJi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -4297,17 +4297,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ath. Bilbao</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -4427,24 +4427,24 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Phase 3 status was upstream_blocked.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:n12plBB7</t>
+          <t>flashscore:nmmS8WHr</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4454,17 +4454,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -4591,17 +4591,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:0OhvAhYQ</t>
+          <t>flashscore:h0IS6Ane</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4611,17 +4611,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -4748,17 +4748,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>flashscore:K8ZA4Wel</t>
+          <t>flashscore:prPnPy9r</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4768,17 +4768,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -4905,17 +4905,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>flashscore:YFVo6qXh</t>
+          <t>flashscore:IXv8WJG8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4925,17 +4925,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5062,17 +5062,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>flashscore:C0sw852t</t>
+          <t>flashscore:r1cGQTSk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -5082,17 +5082,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -5212,24 +5212,24 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>flashscore:llRR0leD</t>
+          <t>flashscore:OhrGQlpm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -5239,17 +5239,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -5369,24 +5369,24 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>Phase 3 status was upstream_blocked.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>flashscore:ttZg4N15</t>
+          <t>flashscore:xbwdLg87</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5396,17 +5396,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -5533,17 +5533,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>flashscore:hMXI2AQ0</t>
+          <t>flashscore:QcrGUcoL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5553,17 +5553,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vallecano</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -5690,17 +5690,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>flashscore:YH84GNJi</t>
+          <t>flashscore:IeNfNFwe</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5710,17 +5710,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Paris FC</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -5840,24 +5840,24 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>flashscore:nmmS8WHr</t>
+          <t>flashscore:44Vsqc0E</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5867,17 +5867,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -6004,17 +6004,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>flashscore:h0IS6Ane</t>
+          <t>flashscore:SduXBE3E</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -6024,17 +6024,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -6161,17 +6161,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>flashscore:prPnPy9r</t>
+          <t>flashscore:vyaxjXte</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -6181,17 +6181,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Ath. Bilbao</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -6311,24 +6311,24 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>flashscore:IXv8WJG8</t>
+          <t>flashscore:n12plBB7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -6338,17 +6338,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -6468,24 +6468,24 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>flashscore:r1cGQTSk</t>
+          <t>flashscore:0OhvAhYQ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -6495,17 +6495,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -6625,24 +6625,24 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>flashscore:OhrGQlpm</t>
+          <t>flashscore:K8ZA4Wel</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -6652,17 +6652,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -6782,24 +6782,24 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>flashscore:xbwdLg87</t>
+          <t>flashscore:YFVo6qXh</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -6809,17 +6809,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6939,24 +6939,24 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>flashscore:z9FNO7c2</t>
+          <t>flashscore:C0sw852t</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6966,17 +6966,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -7096,24 +7096,24 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>flashscore:QcrGUcoL</t>
+          <t>flashscore:llRR0leD</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -7123,17 +7123,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -7253,24 +7253,24 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>flashscore:IeNfNFwe</t>
+          <t>flashscore:ttZg4N15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -7280,17 +7280,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paris FC</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -7417,17 +7417,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>flashscore:44Vsqc0E</t>
+          <t>flashscore:hMXI2AQ0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -7437,17 +7437,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Vallecano</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -7567,24 +7567,24 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>flashscore:SduXBE3E</t>
+          <t>flashscore:z9FNO7c2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -7594,17 +7594,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -7724,14 +7724,14 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
     </row>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-18 04:06:59 ACST</t>
+          <t>2026-05-18 05:06:52 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,7 +174,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:48 ACST</t>
+          <t>2026-05-18 13:54:26 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -184,7 +184,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:lnSvmTkR</t>
+          <t>flashscore:rZdvkkLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -194,17 +194,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -324,14 +324,14 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:48 ACST</t>
+          <t>2026-05-18 13:54:26 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -341,7 +341,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:rZdvkkLE</t>
+          <t>flashscore:lnSvmTkR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -356,12 +356,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -488,7 +488,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:48 ACST</t>
+          <t>2026-05-18 13:54:26 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1137,7 +1137,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:48 ACST</t>
+          <t>2026-05-18 13:54:26 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:lnSvmTkR</t>
+          <t>flashscore:rZdvkkLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1157,17 +1157,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:48 ACST</t>
+          <t>2026-05-18 13:54:26 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:rZdvkkLE</t>
+          <t>flashscore:lnSvmTkR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1451,7 +1451,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:48 ACST</t>
+          <t>2026-05-18 13:54:26 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:48 ACST</t>
+          <t>2026-05-18 13:54:26 ACST</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-18 09:10:02 ACST</t>
+          <t>2026-05-18 12:12:56 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,7 +174,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:26 ACST</t>
+          <t>2026-05-18 17:54:32 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -331,7 +331,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:26 ACST</t>
+          <t>2026-05-18 17:54:32 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,7 +488,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:26 ACST</t>
+          <t>2026-05-18 17:54:32 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1137,7 +1137,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:26 ACST</t>
+          <t>2026-05-18 17:54:32 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1294,7 +1294,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:26 ACST</t>
+          <t>2026-05-18 17:54:32 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1451,7 +1451,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:26 ACST</t>
+          <t>2026-05-18 17:54:32 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:26 ACST</t>
+          <t>2026-05-18 17:54:32 ACST</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-18 12:12:56 ACST</t>
+          <t>2026-05-18 13:54:28 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,37 +174,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 17:54:32 ACST</t>
+          <t>2026-05-19 01:54:16 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:rZdvkkLE</t>
+          <t>flashscore:Gxt6zm15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -323,320 +323,6 @@
         </is>
       </c>
       <c r="AE2" t="inlineStr">
-        <is>
-          <t>Phase 3 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-18 17:54:32 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flashscore:lnSvmTkR</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Phase 3 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-18 17:54:32 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>flashscore:Gxt6zm15</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Burnley</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
         <is>
           <t>Phase 3 status was team_unresolved.</t>
         </is>
@@ -1137,37 +823,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 17:54:32 ACST</t>
+          <t>2026-05-19 01:54:16 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:rZdvkkLE</t>
+          <t>flashscore:Gxt6zm15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1286,320 +972,6 @@
         </is>
       </c>
       <c r="AE2" t="inlineStr">
-        <is>
-          <t>Phase 3 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-18 17:54:32 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flashscore:lnSvmTkR</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Phase 3 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-18 17:54:32 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>flashscore:Gxt6zm15</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Burnley</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
         <is>
           <t>Phase 3 status was team_unresolved.</t>
         </is>
@@ -1632,7 +1004,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 17:54:32 ACST</t>
+          <t>2026-05-19 01:54:16 ACST</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1028,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:28 ACST</t>
+          <t>2026-05-19 01:31:07 ACST</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1040,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1052,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1088,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,7 +174,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 01:54:16 ACST</t>
+          <t>2026-05-19 17:59:55 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -184,27 +184,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:Gxt6zm15</t>
+          <t>flashscore:rkXMW40U</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -323,6 +323,163 @@
         </is>
       </c>
       <c r="AE2" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:59:55 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>flashscore:Uu6uknGb</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Phase 3 status was team_unresolved.</t>
         </is>
@@ -823,7 +980,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 01:54:16 ACST</t>
+          <t>2026-05-19 17:59:55 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -833,27 +990,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:Gxt6zm15</t>
+          <t>flashscore:rkXMW40U</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -972,6 +1129,163 @@
         </is>
       </c>
       <c r="AE2" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:59:55 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>flashscore:Uu6uknGb</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Phase 3 status was team_unresolved.</t>
         </is>
@@ -1004,7 +1318,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-19 01:54:16 ACST</t>
+          <t>2026-05-19 17:59:55 ACST</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1342,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-19 01:31:07 ACST</t>
+          <t>2026-05-19 17:56:58 ACST</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1354,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1366,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1402,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,7 +174,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:55 ACST</t>
+          <t>2026-05-20 01:56:56 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -331,7 +331,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:55 ACST</t>
+          <t>2026-05-20 01:56:56 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -980,7 +980,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:55 ACST</t>
+          <t>2026-05-20 01:56:56 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1137,7 +1137,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:55 ACST</t>
+          <t>2026-05-20 01:56:56 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:55 ACST</t>
+          <t>2026-05-20 01:56:56 ACST</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-19 17:56:58 ACST</t>
+          <t>2026-05-19 19:01:17 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,7 +174,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:56 ACST</t>
+          <t>2026-05-20 05:56:08 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -184,7 +184,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:rkXMW40U</t>
+          <t>flashscore:Uu6uknGb</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -194,17 +194,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -331,7 +331,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:56 ACST</t>
+          <t>2026-05-20 05:56:08 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -341,7 +341,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:Uu6uknGb</t>
+          <t>flashscore:rkXMW40U</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -351,17 +351,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:56 ACST</t>
+          <t>2026-05-20 05:56:08 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:rkXMW40U</t>
+          <t>flashscore:Uu6uknGb</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1000,17 +1000,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1137,7 +1137,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:56 ACST</t>
+          <t>2026-05-20 05:56:08 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:Uu6uknGb</t>
+          <t>flashscore:rkXMW40U</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1157,17 +1157,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:56 ACST</t>
+          <t>2026-05-20 05:56:08 ACST</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-19 19:01:17 ACST</t>
+          <t>2026-05-20 05:34:41 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,37 +174,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 05:56:08 ACST</t>
+          <t>2026-05-20 09:58:04 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:Uu6uknGb</t>
+          <t>thesportsdb:2475105</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>02:15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -331,37 +331,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20 05:56:08 ACST</t>
+          <t>2026-05-20 09:58:04 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:rkXMW40U</t>
+          <t>thesportsdb:2475106</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -481,7 +481,635 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:58:04 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>thesportsdb:2265408</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:58:04 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279766</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:58:04 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279764</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Deportivo Alavés</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
           <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:58:04 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279765</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
@@ -980,37 +1608,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 05:56:08 ACST</t>
+          <t>2026-05-20 09:58:04 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:Uu6uknGb</t>
+          <t>thesportsdb:2475105</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>02:15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1137,37 +1765,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20 05:56:08 ACST</t>
+          <t>2026-05-20 09:58:04 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:rkXMW40U</t>
+          <t>thesportsdb:2475106</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1287,7 +1915,635 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:58:04 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>thesportsdb:2265408</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:58:04 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279766</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:58:04 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279764</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Deportivo Alavés</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
           <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:58:04 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279765</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
@@ -1318,7 +2574,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-20 05:56:08 ACST</t>
+          <t>2026-05-20 09:58:04 ACST</t>
         </is>
       </c>
     </row>
@@ -1342,7 +2598,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-20 05:34:41 ACST</t>
+          <t>2026-05-20 09:41:56 ACST</t>
         </is>
       </c>
     </row>
@@ -1354,7 +2610,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1366,7 +2622,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1402,7 +2658,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,17 +174,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Eliteserien</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:v3i3qEfD</t>
+          <t>flashscore:rJKJ2MZP</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -194,17 +194,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bodo/Glimt</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -324,24 +324,24 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Phase 3 status was upstream_blocked.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>Eliteserien</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:rJKJ2MZP</t>
+          <t>flashscore:YobepuNG</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -356,12 +356,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Lilleström</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -481,14 +481,14 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:YobepuNG</t>
+          <t>flashscore:0A1Nl9Wh</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -508,17 +508,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lilleström</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -638,14 +638,14 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Phase 3 status was upstream_blocked.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>flashscore:0A1Nl9Wh</t>
+          <t>flashscore:v3i3qEfD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -665,17 +665,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Bodo/Glimt</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Eliteserien</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:v3i3qEfD</t>
+          <t>flashscore:rJKJ2MZP</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1314,17 +1314,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bodo/Glimt</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1444,24 +1444,24 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Phase 3 status was upstream_blocked.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>Eliteserien</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:rJKJ2MZP</t>
+          <t>flashscore:YobepuNG</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Lilleström</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1601,14 +1601,14 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:YobepuNG</t>
+          <t>flashscore:0A1Nl9Wh</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lilleström</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1758,14 +1758,14 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Phase 3 status was upstream_blocked.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>flashscore:0A1Nl9Wh</t>
+          <t>flashscore:v3i3qEfD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1785,17 +1785,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Bodo/Glimt</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-21 01:54:09 ACST</t>
+          <t>2026-05-21 02:40:21 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,7 +174,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -194,7 +194,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -324,14 +324,14 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -341,7 +341,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:YobepuNG</t>
+          <t>flashscore:0A1Nl9Wh</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -351,17 +351,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lilleström</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -488,7 +488,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:0A1Nl9Wh</t>
+          <t>flashscore:YobepuNG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -508,17 +508,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lilleström</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -638,14 +638,14 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1294,7 +1294,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1444,14 +1444,14 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:YobepuNG</t>
+          <t>flashscore:0A1Nl9Wh</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1471,17 +1471,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lilleström</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1608,7 +1608,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:0A1Nl9Wh</t>
+          <t>flashscore:YobepuNG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lilleström</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1758,14 +1758,14 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-21 02:40:21 ACST</t>
+          <t>2026-05-21 05:54:42 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,7 +174,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 05:57:50 ACST</t>
+          <t>2026-05-21 18:08:48 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -184,27 +184,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:rJKJ2MZP</t>
+          <t>flashscore:zHabevSa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -324,478 +324,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Phase 3 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-21 05:57:50 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flashscore:0A1Nl9Wh</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Aalesund</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Brann</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Phase 3 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-21 05:57:50 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>flashscore:YobepuNG</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Lilleström</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Kristiansund</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Phase 3 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-21 05:57:50 ACST</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>flashscore:v3i3qEfD</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Bodo/Glimt</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Phase 3 status was upstream_blocked.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
@@ -1294,7 +823,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 05:57:50 ACST</t>
+          <t>2026-05-21 18:08:48 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1304,27 +833,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:rJKJ2MZP</t>
+          <t>flashscore:zHabevSa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1444,478 +973,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Phase 3 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-21 05:57:50 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flashscore:0A1Nl9Wh</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Aalesund</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Brann</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Phase 3 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-21 05:57:50 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>flashscore:YobepuNG</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Lilleström</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Kristiansund</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Phase 3 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-21 05:57:50 ACST</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>flashscore:v3i3qEfD</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Bodo/Glimt</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Phase 3 status was upstream_blocked.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1004,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 05:57:50 ACST</t>
+          <t>2026-05-21 18:08:48 ACST</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1028,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-21 05:54:42 ACST</t>
+          <t>2026-05-21 18:02:59 ACST</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1040,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1052,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2030,7 +1088,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,7 +174,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:08:48 ACST</t>
+          <t>2026-05-21 18:22:40 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:08:48 ACST</t>
+          <t>2026-05-21 18:22:40 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:08:48 ACST</t>
+          <t>2026-05-21 18:22:40 ACST</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-21 18:02:59 ACST</t>
+          <t>2026-05-21 18:08:59 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,7 +174,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:22:40 ACST</t>
+          <t>2026-05-22 01:59:19 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:22:40 ACST</t>
+          <t>2026-05-22 01:59:19 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:22:40 ACST</t>
+          <t>2026-05-22 01:59:19 ACST</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-21 18:08:59 ACST</t>
+          <t>2026-05-22 01:30:48 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,7 +174,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 01:59:19 ACST</t>
+          <t>2026-05-22 04:29:40 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -194,7 +194,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 01:59:19 ACST</t>
+          <t>2026-05-22 04:29:40 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Phase 3 status was team_unresolved.</t>
+          <t>Phase 3 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 01:59:19 ACST</t>
+          <t>2026-05-22 04:29:40 ACST</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22 01:30:48 ACST</t>
+          <t>2026-05-22 03:28:55 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,157 +174,471 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 04:29:40 ACST</t>
+          <t>2026-05-22 17:57:58 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>flashscore:fXvLSp0T</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Machida</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Urawa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:57:58 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>flashscore:zHabevSa</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Elfsborg</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Mjallby</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>flashscore:l6SULOIj</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Djurgarden</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>upstream_blocked</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Phase 3 status was upstream_blocked.</t>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:57:58 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>flashscore:ln2VQVwR</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
@@ -823,157 +1137,471 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 04:29:40 ACST</t>
+          <t>2026-05-22 17:57:58 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>flashscore:fXvLSp0T</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Machida</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Urawa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:57:58 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>flashscore:zHabevSa</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Elfsborg</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Mjallby</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>flashscore:l6SULOIj</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Djurgarden</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>upstream_blocked</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Phase 3 status was upstream_blocked.</t>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:57:58 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>flashscore:ln2VQVwR</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1632,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 04:29:40 ACST</t>
+          <t>2026-05-22 17:57:58 ACST</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1656,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22 03:28:55 ACST</t>
+          <t>2026-05-22 17:25:45 ACST</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1668,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1680,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1716,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,7 +174,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:58 ACST</t>
+          <t>2026-05-22 18:59:47 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -331,7 +331,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:58 ACST</t>
+          <t>2026-05-22 18:59:47 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,7 +488,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:58 ACST</t>
+          <t>2026-05-22 18:59:47 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1137,7 +1137,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:58 ACST</t>
+          <t>2026-05-22 18:59:47 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1294,7 +1294,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:58 ACST</t>
+          <t>2026-05-22 18:59:47 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1451,7 +1451,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:58 ACST</t>
+          <t>2026-05-22 18:59:47 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:58 ACST</t>
+          <t>2026-05-22 18:59:47 ACST</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22 17:25:45 ACST</t>
+          <t>2026-05-22 18:14:10 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase4_Predictions.xlsx
+++ b/docs/agent-system/outputs/Phase4_Predictions.xlsx
@@ -174,37 +174,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:47 ACST</t>
+          <t>2026-06-05 19:29:23 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J1 League</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:fXvLSp0T</t>
+          <t>flashscore:EsE6FP8c</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Machida</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Urawa</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -324,44 +324,44 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Phase 3 status was upstream_blocked.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:47 ACST</t>
+          <t>2026-06-05 19:29:23 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:l6SULOIj</t>
+          <t>flashscore:AqnFNaI5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Djurgarden</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -488,37 +488,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:47 ACST</t>
+          <t>2026-06-05 19:29:23 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:ln2VQVwR</t>
+          <t>flashscore:f55NQIsS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -637,6 +637,2832 @@
         </is>
       </c>
       <c r="AE4" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>flashscore:WCykuuhU</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>flashscore:A7YX1Ha6</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>flashscore:j1djEBZR</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>flashscore:MHMpxPfo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Liberia</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>flashscore:b1x9Omno</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>flashscore:UTlT8H3E</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>flashscore:GCkooKhS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tajikistan</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>flashscore:x0ey9SdL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Belarus</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>flashscore:lIwBomFD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>flashscore:G4u3m9p1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>flashscore:Cv3iCkuq</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Moldova</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>flashscore:fJz9NRBE</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Burkina Faso</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>flashscore:rPCLHBHL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>San Marino</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>flashscore:bZVLx0FO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>03:15</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>flashscore:jDnBGlak</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Azerbaijan</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>flashscore:fNtF7Ai4</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Niger</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>flashscore:8xq71Zel</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Central Africa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Togo</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>flashscore:WjtZbjct</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Mauritania</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
         <is>
           <t>Phase 3 status was team_unresolved.</t>
         </is>
@@ -1137,37 +3963,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:47 ACST</t>
+          <t>2026-06-05 19:29:23 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J1 League</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:fXvLSp0T</t>
+          <t>flashscore:EsE6FP8c</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Machida</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Urawa</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1287,44 +4113,44 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Phase 3 status was upstream_blocked.</t>
+          <t>Phase 3 status was team_unresolved.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:47 ACST</t>
+          <t>2026-06-05 19:29:23 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:l6SULOIj</t>
+          <t>flashscore:AqnFNaI5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Djurgarden</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1451,37 +4277,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:47 ACST</t>
+          <t>2026-06-05 19:29:23 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:ln2VQVwR</t>
+          <t>flashscore:f55NQIsS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1600,6 +4426,2832 @@
         </is>
       </c>
       <c r="AE4" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>flashscore:WCykuuhU</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>flashscore:A7YX1Ha6</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>flashscore:j1djEBZR</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>flashscore:MHMpxPfo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Liberia</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>flashscore:b1x9Omno</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>flashscore:UTlT8H3E</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>flashscore:GCkooKhS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tajikistan</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>flashscore:x0ey9SdL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Belarus</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>flashscore:lIwBomFD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>flashscore:G4u3m9p1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>flashscore:Cv3iCkuq</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Moldova</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>flashscore:fJz9NRBE</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Burkina Faso</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Phase 3 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>flashscore:rPCLHBHL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>San Marino</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>flashscore:bZVLx0FO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>03:15</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>flashscore:jDnBGlak</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Azerbaijan</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>flashscore:fNtF7Ai4</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Niger</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>flashscore:8xq71Zel</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Central Africa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Togo</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Phase 3 status was team_unresolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>flashscore:WjtZbjct</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Mauritania</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
         <is>
           <t>Phase 3 status was team_unresolved.</t>
         </is>
@@ -1632,7 +7284,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:47 ACST</t>
+          <t>2026-06-05 19:29:23 ACST</t>
         </is>
       </c>
     </row>
@@ -1656,7 +7308,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22 18:14:10 ACST</t>
+          <t>2026-06-05 19:04:56 ACST</t>
         </is>
       </c>
     </row>
@@ -1668,7 +7320,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1680,7 +7332,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1716,7 +7368,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
     </row>
